--- a/AAII_Financials/Quarterly/QSJC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSJC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>QSJC</t>
   </si>
@@ -752,7 +752,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>-500</v>
+        <v>500</v>
       </c>
       <c r="E9" s="3">
         <v>700</v>
@@ -784,7 +784,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
@@ -968,8 +968,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
+      <c r="D17" s="3">
+        <v>600</v>
       </c>
       <c r="E17" s="3">
         <v>900</v>
@@ -1000,8 +1000,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
+      <c r="D18" s="3">
+        <v>0</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -1046,8 +1046,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1078,8 +1078,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
@@ -1142,8 +1142,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
+      <c r="D23" s="3">
+        <v>0</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -1238,8 +1238,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
+      <c r="D26" s="3">
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <v>0</v>
@@ -1270,8 +1270,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
+      <c r="D27" s="3">
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
@@ -1430,8 +1430,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1462,8 +1462,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
+      <c r="D33" s="3">
+        <v>0</v>
       </c>
       <c r="E33" s="3">
         <v>0</v>
@@ -1526,8 +1526,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
+      <c r="D35" s="3">
+        <v>0</v>
       </c>
       <c r="E35" s="3">
         <v>0</v>
@@ -1847,8 +1847,8 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>100</v>
       </c>
       <c r="E48" s="3">
         <v>100</v>
@@ -2790,8 +2790,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
+      <c r="D81" s="3">
+        <v>0</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
@@ -2839,23 +2839,23 @@
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3028,8 +3028,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>-700</v>
       </c>
       <c r="E89" s="3">
         <v>1000</v>
@@ -3075,10 +3075,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/QSJC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSJC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>QSJC</t>
   </si>
@@ -656,84 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
@@ -746,26 +753,32 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
         <v>500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>5</v>
       </c>
@@ -778,8 +791,14 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -787,16 +806,16 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
+      <c r="H10" s="3">
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>5</v>
@@ -810,8 +829,14 @@
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +849,10 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,8 +883,14 @@
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,8 +921,14 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -920,8 +959,14 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -934,8 +979,8 @@
       <c r="F15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>5</v>
@@ -946,14 +991,20 @@
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -963,25 +1014,27 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E17" s="3">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="F17" s="3">
         <v>600</v>
       </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I17" s="3">
         <v>0</v>
@@ -995,26 +1048,32 @@
       <c r="L17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
         <v>0</v>
       </c>
@@ -1027,8 +1086,14 @@
       <c r="L18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1041,8 +1106,10 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1073,40 +1140,52 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1137,26 +1216,32 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
@@ -1169,8 +1254,14 @@
       <c r="L23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1201,8 +1292,14 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1233,26 +1330,32 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
@@ -1265,26 +1368,32 @@
       <c r="L26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
         <v>0</v>
       </c>
@@ -1297,8 +1406,14 @@
       <c r="L27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1329,8 +1444,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1361,8 +1482,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1393,8 +1520,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1425,8 +1558,14 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1457,26 +1596,32 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
         <v>0</v>
       </c>
@@ -1489,8 +1634,14 @@
       <c r="L33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1521,26 +1672,32 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
         <v>0</v>
       </c>
@@ -1553,45 +1710,57 @@
       <c r="L35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1604,8 +1773,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1618,28 +1789,30 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>400</v>
+      </c>
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -1650,8 +1823,14 @@
       <c r="L41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1682,8 +1861,14 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1694,14 +1879,14 @@
         <v>0</v>
       </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>5</v>
       </c>
@@ -1714,8 +1899,14 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1723,17 +1914,17 @@
         <v>1200</v>
       </c>
       <c r="E44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G44" s="3">
         <v>1100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>700</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>5</v>
       </c>
@@ -1746,8 +1937,14 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1755,17 +1952,17 @@
         <v>1700</v>
       </c>
       <c r="E45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
@@ -1778,25 +1975,31 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="E46" s="3">
-        <v>4000</v>
+        <v>3400</v>
       </c>
       <c r="F46" s="3">
         <v>3300</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="I46" s="3">
         <v>0</v>
@@ -1810,8 +2013,14 @@
       <c r="L46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1842,8 +2051,14 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1853,11 +2068,11 @@
       <c r="E48" s="3">
         <v>100</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
+      <c r="F48" s="3">
+        <v>100</v>
+      </c>
+      <c r="G48" s="3">
+        <v>100</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
@@ -1874,8 +2089,14 @@
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1891,23 +2112,29 @@
       <c r="G49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1938,8 +2165,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1970,8 +2203,14 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2002,8 +2241,14 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2034,26 +2279,32 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G54" s="3">
         <v>4100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3300</v>
       </c>
-      <c r="G54" s="3">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3">
-        <v>0</v>
-      </c>
       <c r="I54" s="3">
         <v>0</v>
       </c>
@@ -2066,8 +2317,14 @@
       <c r="L54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2080,8 +2337,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2094,40 +2353,48 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
+      <c r="K57" s="3">
+        <v>0</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2158,8 +2425,14 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2167,19 +2440,19 @@
         <v>4400</v>
       </c>
       <c r="E59" s="3">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="F59" s="3">
         <v>4400</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="H59" s="3">
-        <v>100</v>
+        <v>4400</v>
       </c>
       <c r="I59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
@@ -2190,31 +2463,37 @@
       <c r="L59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4400</v>
       </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
         <v>200</v>
-      </c>
-      <c r="I60" s="3">
-        <v>100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>100</v>
       </c>
       <c r="K60" s="3">
         <v>100</v>
@@ -2222,8 +2501,14 @@
       <c r="L60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3">
+        <v>100</v>
+      </c>
+      <c r="N60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2254,8 +2539,14 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2286,8 +2577,14 @@
       <c r="L62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2318,8 +2615,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2350,8 +2653,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2382,31 +2691,37 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F66" s="3">
         <v>4600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4400</v>
       </c>
-      <c r="G66" s="3">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3">
         <v>200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>100</v>
       </c>
       <c r="K66" s="3">
         <v>100</v>
@@ -2414,8 +2729,14 @@
       <c r="L66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3">
+        <v>100</v>
+      </c>
+      <c r="N66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2428,8 +2749,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2460,8 +2783,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2492,8 +2821,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2524,8 +2859,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2556,31 +2897,37 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1300</v>
+        <v>-1500</v>
       </c>
       <c r="E72" s="3">
         <v>-1400</v>
       </c>
       <c r="F72" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G72" s="3">
         <v>-1400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I72" s="3">
         <v>-200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-200</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-100</v>
       </c>
       <c r="K72" s="3">
         <v>-100</v>
@@ -2588,8 +2935,14 @@
       <c r="L72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2620,8 +2973,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2652,8 +3011,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2684,31 +3049,37 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F76" s="3">
         <v>-1100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-1100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-1200</v>
       </c>
-      <c r="G76" s="3">
-        <v>0</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
         <v>-200</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-100</v>
       </c>
       <c r="K76" s="3">
         <v>-100</v>
@@ -2716,8 +3087,14 @@
       <c r="L76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2748,63 +3125,75 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
@@ -2817,8 +3206,14 @@
       <c r="L81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2831,19 +3226,21 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>5</v>
@@ -2857,14 +3254,20 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2895,8 +3298,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2927,8 +3336,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2959,8 +3374,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2991,8 +3412,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3023,29 +3450,35 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
@@ -3055,8 +3488,14 @@
       <c r="L89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3069,8 +3508,10 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3078,11 +3519,11 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -3101,8 +3542,14 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3133,8 +3580,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3165,40 +3618,52 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3211,8 +3676,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3243,8 +3710,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3275,8 +3748,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3307,8 +3786,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3339,29 +3824,35 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -3371,8 +3862,14 @@
       <c r="L100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3380,16 +3877,16 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>5</v>
@@ -3403,26 +3900,32 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -3433,6 +3936,12 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QSJC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QSJC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>QSJC</t>
   </si>
@@ -656,97 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
@@ -759,8 +767,14 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -768,23 +782,23 @@
         <v>100</v>
       </c>
       <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
@@ -797,31 +811,37 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>200</v>
+      </c>
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -835,8 +855,14 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +877,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +917,14 @@
       <c r="N12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,31 +961,37 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -965,31 +1005,37 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -997,14 +1043,20 @@
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,31 +1068,33 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3">
         <v>300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>200</v>
-      </c>
-      <c r="F17" s="3">
-        <v>600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>900</v>
       </c>
       <c r="H17" s="3">
         <v>600</v>
       </c>
       <c r="I17" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J17" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -1054,8 +1108,14 @@
       <c r="N17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1066,19 +1126,19 @@
         <v>-100</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H18" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
         <v>0</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K18" s="3">
         <v>0</v>
@@ -1092,8 +1152,14 @@
       <c r="N18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1174,10 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1146,69 +1214,81 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <v>-100</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
+      <c r="K21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
+      <c r="M21" s="3">
+        <v>0</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1222,8 +1302,14 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1234,20 +1320,20 @@
         <v>-100</v>
       </c>
       <c r="F23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
         <v>0</v>
       </c>
@@ -1260,31 +1346,37 @@
       <c r="N23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1298,8 +1390,14 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,8 +1434,14 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1348,20 +1452,20 @@
         <v>-100</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
         <v>0</v>
       </c>
@@ -1374,8 +1478,14 @@
       <c r="N26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1386,20 +1496,20 @@
         <v>-100</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
         <v>0</v>
       </c>
@@ -1412,8 +1522,14 @@
       <c r="N27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1566,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1610,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1654,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,8 +1698,14 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1602,8 +1742,14 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1614,20 +1760,20 @@
         <v>-100</v>
       </c>
       <c r="F33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
         <v>0</v>
       </c>
@@ -1640,8 +1786,14 @@
       <c r="N33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,8 +1830,14 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1690,20 +1848,20 @@
         <v>-100</v>
       </c>
       <c r="F35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
         <v>0</v>
       </c>
@@ -1716,51 +1874,63 @@
       <c r="N35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1945,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,34 +1963,36 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
+      <c r="K41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -1829,8 +2003,14 @@
       <c r="N41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,8 +2047,14 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1885,14 +2071,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
@@ -1905,32 +2091,38 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1200</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1300</v>
       </c>
       <c r="F44" s="3">
         <v>1200</v>
       </c>
       <c r="G44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I44" s="3">
         <v>1100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>700</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
@@ -1943,32 +2135,38 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>1700</v>
       </c>
       <c r="G45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
         <v>0</v>
       </c>
@@ -1981,31 +2179,37 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F46" s="3">
         <v>3000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3400</v>
-      </c>
-      <c r="F46" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>4000</v>
       </c>
       <c r="H46" s="3">
         <v>3300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2019,31 +2223,37 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2057,8 +2267,14 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2074,11 +2290,11 @@
       <c r="G48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
+      <c r="H48" s="3">
+        <v>100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>100</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -2095,46 +2311,58 @@
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2399,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,31 +2443,37 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2247,8 +2487,14 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,32 +2531,38 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F54" s="3">
         <v>3200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3300</v>
       </c>
-      <c r="I54" s="3">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
-      </c>
       <c r="K54" s="3">
         <v>0</v>
       </c>
@@ -2323,8 +2575,14 @@
       <c r="N54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3">
+        <v>0</v>
+      </c>
+      <c r="P54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2597,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,46 +2615,54 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2431,34 +2699,40 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4400</v>
+        <v>3000</v>
       </c>
       <c r="E59" s="3">
-        <v>4500</v>
+        <v>2800</v>
       </c>
       <c r="F59" s="3">
         <v>4400</v>
       </c>
       <c r="G59" s="3">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="H59" s="3">
         <v>4400</v>
       </c>
       <c r="I59" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="J59" s="3">
-        <v>100</v>
+        <v>4400</v>
       </c>
       <c r="K59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
@@ -2469,37 +2743,43 @@
       <c r="N59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3">
+        <v>100</v>
+      </c>
+      <c r="P59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F60" s="3">
         <v>4400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4400</v>
       </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3">
         <v>200</v>
-      </c>
-      <c r="K60" s="3">
-        <v>100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>100</v>
       </c>
       <c r="M60" s="3">
         <v>100</v>
@@ -2507,8 +2787,14 @@
       <c r="N60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>100</v>
+      </c>
+      <c r="P60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2545,31 +2831,37 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2583,8 +2875,14 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2919,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2963,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,37 +3007,43 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F66" s="3">
         <v>4400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4400</v>
       </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3">
         <v>200</v>
-      </c>
-      <c r="K66" s="3">
-        <v>100</v>
-      </c>
-      <c r="L66" s="3">
-        <v>100</v>
       </c>
       <c r="M66" s="3">
         <v>100</v>
@@ -2735,8 +3051,14 @@
       <c r="N66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3">
+        <v>100</v>
+      </c>
+      <c r="P66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3073,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3113,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3157,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3201,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3245,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-1300</v>
       </c>
       <c r="G72" s="3">
         <v>-1400</v>
       </c>
       <c r="H72" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I72" s="3">
         <v>-1400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K72" s="3">
         <v>-200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-200</v>
       </c>
-      <c r="K72" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-100</v>
-      </c>
       <c r="M72" s="3">
         <v>-100</v>
       </c>
       <c r="N72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3333,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3377,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3421,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-1300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-1200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-1100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-1100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-1200</v>
       </c>
-      <c r="I76" s="3">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3">
         <v>-200</v>
       </c>
-      <c r="K76" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L76" s="3">
-        <v>-100</v>
-      </c>
       <c r="M76" s="3">
         <v>-100</v>
       </c>
       <c r="N76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,51 +3509,63 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3186,20 +3576,20 @@
         <v>-100</v>
       </c>
       <c r="F81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
         <v>0</v>
       </c>
@@ -3212,8 +3602,14 @@
       <c r="N81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,8 +3624,10 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3239,17 +3637,17 @@
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>5</v>
@@ -3260,14 +3658,20 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3708,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3752,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3796,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3840,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,35 +3884,41 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
@@ -3494,8 +3928,14 @@
       <c r="N89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,19 +3950,21 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -3531,10 +3973,10 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3548,8 +3990,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4034,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +4078,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,31 +4144,33 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3716,8 +4184,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4228,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4272,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,8 +4316,14 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3839,25 +4331,25 @@
         <v>100</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -3868,8 +4360,14 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3877,19 +4375,19 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>5</v>
@@ -3906,32 +4404,38 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
@@ -3942,6 +4446,12 @@
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>
